--- a/data/trans_orig/IP16B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Provincia-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71037</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75944</t>
+          <t>76337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148770</t>
+          <t>148895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152198</t>
+          <t>152219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117583</t>
+          <t>117992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>124899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116601</t>
+          <t>117157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124801</t>
+          <t>124815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>238200</t>
+          <t>238477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248474</t>
+          <t>248744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56031</t>
+          <t>56589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64979</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122232</t>
+          <t>122291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>60665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65259</t>
+          <t>65239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65881</t>
+          <t>65074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128867</t>
+          <t>128648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134916</t>
+          <t>134763</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43886</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54623</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99844</t>
+          <t>99847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115627</t>
+          <t>116122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121700</t>
+          <t>121719</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146804</t>
+          <t>147487</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153380</t>
+          <t>153426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267372</t>
+          <t>266966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274541</t>
+          <t>274384</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>127515</t>
+          <t>127330</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149901</t>
+          <t>150249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155011</t>
+          <t>155000</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>280166</t>
+          <t>279961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>286181</t>
+          <t>285895</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>641840</t>
+          <t>641857</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>651686</t>
+          <t>651919</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>730668</t>
+          <t>730188</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>741879</t>
+          <t>741701</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1375720</t>
+          <t>1375972</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1391436</t>
+          <t>1391602</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>63353</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61640</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>72811</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>70983</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>56066</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53963</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>56481</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>95,54%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>78404</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>76337</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>79366</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>195</t>
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>151215</t>
+          <t>119419</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148895</t>
+          <t>117655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152219</t>
+          <t>120269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2299</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2518</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>110911</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>106346</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>113432</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>122444</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>117992</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>124899</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>121976</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117157</t>
+          <t>92201</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124815</t>
+          <t>98545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>244420</t>
+          <t>207392</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>238477</t>
+          <t>201974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248744</t>
+          <t>211108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9191</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3286</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7738</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115537</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115537</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115537</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125730</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125730</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125730</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252930</t>
+          <t>214880</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252930</t>
+          <t>214880</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252930</t>
+          <t>214880</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>58751</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57453</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59064</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>57871</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56589</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>56204</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>53997</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>66401</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>64206</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>66782</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>195</t>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>124272</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122291</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>115622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>354</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>668</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59064</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59064</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59064</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66782</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66782</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66782</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>115622</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>115622</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>115622</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63773</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60381</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64804</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>63600</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>60665</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65239</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68997</t>
+          <t>65137</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65074</t>
+          <t>61875</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70241</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>132597</t>
+          <t>128911</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128648</t>
+          <t>125457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134763</t>
+          <t>130749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5411</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>64804</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>64804</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>64804</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>66076</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>66076</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>66076</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70241</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70241</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70241</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>136317</t>
+          <t>132089</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136317</t>
+          <t>132089</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136317</t>
+          <t>132089</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>35608</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>139</t>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,74 +2435,74 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48694</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>47453</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>45817</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>44369</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>45508</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>44299</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>45766</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>55828</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>54557</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>56186</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>170</t>
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>101645</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99847</t>
+          <t>92705</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>506</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,74 +2778,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>137657</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>133697</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>139290</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>120183</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>116122</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>121719</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>117967</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>113816</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>119603</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>151519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>147487</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>153426</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>342</t>
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>271702</t>
+          <t>255624</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266966</t>
+          <t>250789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274384</t>
+          <t>258275</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6260</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>6254</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2281</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6432</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2509</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>6541</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>139957</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>139957</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>139957</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>122376</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>122376</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>122376</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154028</t>
+          <t>120248</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154028</t>
+          <t>120248</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154028</t>
+          <t>120248</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>276404</t>
+          <t>260205</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276404</t>
+          <t>260205</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>276404</t>
+          <t>260205</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,74 +3121,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>156251</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>153459</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>157935</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>98,55%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>130413</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>127330</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>139447</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>137063</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>140497</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>153337</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>150249</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>155000</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>390</t>
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>283750</t>
+          <t>295698</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>279961</t>
+          <t>292000</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>285895</t>
+          <t>297529</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5093</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4289</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5813</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>158552</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>158552</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>158552</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156062</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156062</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156062</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>287681</t>
+          <t>299049</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>287681</t>
+          <t>299049</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>287681</t>
+          <t>299049</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>678968</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>672766</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>683176</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>647654</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>641857</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>651919</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>612419</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>606483</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>616045</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>97,54%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>737181</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>730188</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>741701</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1384834</t>
+          <t>1291387</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1375972</t>
+          <t>1284136</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1391602</t>
+          <t>1297813</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -3577,74 +3577,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>17814</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>10378</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>16175</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>5741</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>15303</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>13403</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>8883</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>20396</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
